--- a/template/linearity_lbc_random.xlsx
+++ b/template/linearity_lbc_random.xlsx
@@ -546,7 +546,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -650,7 +650,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -1032,10 +1032,6 @@
         <f>AVERAGE(F4:F1015)</f>
         <v/>
       </c>
-      <c r="G1">
-        <f>IF(ABS(D4)&gt;3,160/2^19,160/SQRT(2)/2^19)</f>
-        <v/>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n"/>
@@ -1074,11 +1070,7 @@
           <t>設定DAC値</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>+2^15</t>
-        </is>
-      </c>
+      <c r="B3" s="11" t="n"/>
       <c r="F3" s="14" t="inlineStr">
         <is>
           <t>INL(LSB)</t>

--- a/template/linearity_lbc_random.xlsx
+++ b/template/linearity_lbc_random.xlsx
@@ -15,12 +15,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000_);[Red]\(0.0000\)"/>
     <numFmt numFmtId="165" formatCode="0.00_ "/>
     <numFmt numFmtId="166" formatCode="0.000000_ "/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -55,6 +57,9 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -76,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,6 +121,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -999,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="13.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1032,6 +1040,12 @@
         <f>AVERAGE(F4:F1015)</f>
         <v/>
       </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>GAIN</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n"/>
@@ -1063,6 +1077,12 @@
           <t>測定順</t>
         </is>
       </c>
+      <c r="J2" s="19" t="inlineStr">
+        <is>
+          <t>OFFSET</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -1082,6 +1102,12 @@
         </is>
       </c>
       <c r="H3" s="13" t="n"/>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>MaxErr</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
